--- a/data/seed/portfolio/L-2025-9700/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-9700/vypiska_2026-07_09.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Выписка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ko'chirma" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -56,7 +53,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -423,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:I175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -435,7 +434,6 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,270 +446,217 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ВЫПИСКА ПО РАСЧЕТНОМУ СЧЕТУ № 20208000772710236001</t>
+          <t>HISOB RAQAMIDAN KO'CHIRMA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Клиент: Durdona Qurilish AJ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ИНН: 349637466</t>
+          <t>Hisob raqami: 20208000772710236001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Период: с 01.07.2026 по 30.09.2026</t>
+          <t>Mijoz: Durdona Qurilish AJ, STIR 349637466</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Входящий остаток на 01.07.2026:</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
+          <t>Davr: 01.07.2026 - 30.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Davr boshidagi qoldiq:</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>975300000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Дата</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>№ док.</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Дебет</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>Наименование контрагента</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>ИНН контрагента</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>Счет контрагента</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>МФО банка</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>Назначение платежа</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>Остаток</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B8" t="n">
-        <v>100</v>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n">
-        <v>103771000</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>393733763</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>20208000239026399001</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №65/26 от 01.07.2026</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1079071000</v>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sana</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Hujjat №</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Aylanma</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Kontragent</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>To'lov maqsadi</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46206</v>
-      </c>
-      <c r="B9" t="n">
-        <v>101</v>
-      </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n">
-        <v>222692000</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ziyo Savdo XK</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>313862891</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>20208000007893321001</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №252/26 от 03.07.2026</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>1301763000</v>
-      </c>
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Debet</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Kredit</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Nomi</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>STIR</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Hisob raqami</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46208</v>
-      </c>
-      <c r="B10" t="n">
-        <v>102</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>250500000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>77078000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9700)</t>
+          <t>Shahrisabz Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>16307000349637466417</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9700 bo'yicha navbatdagi to'lov (07.2026)</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>1051263000</v>
+          <t>Оплата за продукцию по дог. №296/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46209</v>
-      </c>
-      <c r="B11" t="n">
-        <v>103</v>
-      </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>279235000</v>
-      </c>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>25045000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Toshkent Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>257855048</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000908674031001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №207 от 06.07.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>1330498000</v>
+          <t>Оплата за транспортные услуги по дог. №262/26</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46209</v>
-      </c>
-      <c r="B12" t="n">
-        <v>104</v>
-      </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>68808000</v>
-      </c>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>28462000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oqtosh Qog'oz MChJ</t>
+          <t>Bog'ishamol Non XK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>209981350</t>
+          <t>299782426</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000017396323001</t>
+          <t>20208000824202015001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -721,672 +666,684 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №75/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>1399306000</v>
+          <t>Оплата за упаковочные материалы, с/ф №7188</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46209</v>
-      </c>
-      <c r="B13" t="n">
-        <v>105</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>402096000</v>
+        <v>87290000</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Bog'ishamol Non XK</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>299782426</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000824202015001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №4146</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>43327000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Qo'qon Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>287941488</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20208000393120511001</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №5538</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>59156000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Zarafshon Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>323675136</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>20208000489984699001</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>01204</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Iyun oyi uchun ish haqi, reestr №1008</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>997210000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46210</v>
-      </c>
-      <c r="B14" t="n">
-        <v>106</v>
-      </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>70051000</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Ziyo Savdo XK</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>313862891</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>20208000007893321001</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №4414 от 07.07.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1067261000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46210</v>
-      </c>
-      <c r="B15" t="n">
-        <v>107</v>
-      </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>57836000</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>393733763</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>20208000239026399001</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №46/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1125097000</v>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №177/26</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46211</v>
-      </c>
-      <c r="B16" t="n">
-        <v>108</v>
-      </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>101064000</v>
-      </c>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>05.07.2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>250500000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>313862891</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9700)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>16307000349637466417</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №229/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>1226161000</v>
+          <t>Kredit shartnomasi L-2025-9700 bo'yicha navbatdagi to'lov (07.2026)</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46211</v>
-      </c>
-      <c r="B17" t="n">
-        <v>109</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>320839000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>174706000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Afrosiyob Mebel MChJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>301022287</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000499149822001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №85/26</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>905322000</v>
+          <t>Оплата по счет-фактуре №1997 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46212</v>
-      </c>
-      <c r="B18" t="n">
-        <v>110</v>
-      </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>96300000</v>
-      </c>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>20772000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oqtosh Qog'oz MChJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>209981350</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000017396323001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2481 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1001622000</v>
+          <t>Оплата за сырье по договору №87/26 от 06.07.2026, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46212</v>
-      </c>
-      <c r="B19" t="n">
-        <v>111</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>30528000</v>
+        <v>101680000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish Materiallari MChJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>205823675</t>
+          <t>372985001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000365489984001</t>
+          <t>20208000944466651001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №33/25</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>971094000</v>
+          <t>Оплата за сырье по дог. №54/26 от 06.07.2026, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B20" t="n">
-        <v>112</v>
-      </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>345476000</v>
-      </c>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>260967000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №8/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>1316570000</v>
+          <t>Оплата за транспортные услуги по договору №152/26</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B21" t="n">
-        <v>113</v>
-      </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>83460000</v>
-      </c>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>402096000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>393733763</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №643</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1400030000</v>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №9267</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46216</v>
-      </c>
-      <c r="B22" t="n">
-        <v>114</v>
-      </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>681077000</v>
-      </c>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>07.07.2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>33313000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Andijon Metall XK</t>
+          <t>Sharq Mato MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>321109101</t>
+          <t>334390146</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000775039704001</t>
+          <t>20208000728720389001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9323 от 13.07.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>2081107000</v>
+          <t>Оплата за сырье по договору №114/26 от 07.07.2026, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>46216</v>
-      </c>
-      <c r="B23" t="n">
-        <v>115</v>
-      </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>182436000</v>
-      </c>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>07.07.2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>54093000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Andijon Metall XK</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>321109101</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000775039704001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shartnoma №115/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>2263543000</v>
+          <t>Предоплата за материалы по договору №1/26</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>46216</v>
-      </c>
-      <c r="B24" t="n">
-        <v>116</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>80865000</v>
+        <v>259700000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Andijon Metall XK</t>
+          <t>Kamalak Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>321109101</t>
+          <t>283030724</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000775039704001</t>
+          <t>20208000808871746001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3088 от 13.07.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>2344408000</v>
+          <t>Shartnoma №85/26 bo'yicha oldindan to'lov</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>46216</v>
-      </c>
-      <c r="B25" t="n">
-        <v>117</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>642497000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>89026000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>210910127</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000503970463001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №229/26</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>1701911000</v>
+          <t>Mahsulot uchun to'lov, shartnoma №258/26, QQS 12%</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B26" t="n">
-        <v>118</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>54831000</v>
+        <v>30528000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Samarqand Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>386067474</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000938342519001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>1647080000</v>
+          <t>Ijara haqi iyul oyi uchun, shartnoma №98/21</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B27" t="n">
-        <v>119</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>54831000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>516914000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>1592249000</v>
+          <t>Оплата за товар по счет-фактуре №3926 от 10.07.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>46218</v>
-      </c>
-      <c r="B28" t="n">
-        <v>120</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>247692000</v>
+        <v>34492000</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Termiz Metall XK</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>355787594</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000548335441001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №4802</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>1344557000</v>
+          <t>Оплата за товары согласно счет-фактуре №5992</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>46219</v>
-      </c>
-      <c r="B29" t="n">
-        <v>121</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>577226000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>1158244000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>235186774</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000214999655001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1396,157 +1353,161 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №22/26</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>767331000</v>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8898</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>46220</v>
-      </c>
-      <c r="B30" t="n">
-        <v>122</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>48361000</v>
+        <v>359636000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>313862891</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4085 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>815692000</v>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №19/26 ОТ 13.07.2026</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B31" t="n">
-        <v>123</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>76177000</v>
+        <v>148372000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1439 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>891869000</v>
+          <t>Shartnoma №234/26 bo'yicha oldindan to'lov</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B32" t="n">
-        <v>124</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>205418000</v>
+        <v>254370000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>372985001</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000944466651001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8625</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>686451000</v>
+          <t>Оплата за сырье по дог. №257/26 от 13.07.2026, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>46226</v>
-      </c>
-      <c r="B33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>92243000</v>
-      </c>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>333648000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>372985001</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000944466651001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1556,772 +1517,802 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №76/26 ОТ 23.07.2026</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>778694000</v>
+          <t>Оплата за транспортные услуги по договору №93/26</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>46226</v>
-      </c>
-      <c r="B34" t="n">
-        <v>126</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>51316000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>314073000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Durdona Polimer XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>251039952</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000529104342001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>727378000</v>
+          <t>Оплата за продукцию по дог. №94/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>46226</v>
-      </c>
-      <c r="B35" t="n">
-        <v>127</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>542280000</v>
+        <v>54831000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Termiz Metall XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>355787594</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000548335441001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5282</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>185098000</v>
+          <t>Уплата социального налога за июнь</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B36" t="n">
-        <v>128</v>
-      </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>501766000</v>
-      </c>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>54831000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4646 от 24.07.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>686864000</v>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B37" t="n">
-        <v>129</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>79724000</v>
+        <v>141252000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Andijon Metall XK</t>
+          <t>Durdona Polimer XK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>321109101</t>
+          <t>251039952</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000775039704001</t>
+          <t>20208000529104342001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9080 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>766588000</v>
+          <t>Предоплата за товар по договору №167/26 от 17.07.2026</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B38" t="n">
-        <v>130</v>
-      </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>687049000</v>
-      </c>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>303175000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olmaliq Ip-Kalava MChJ</t>
+          <t>Toshkent Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>395278409</t>
+          <t>257855048</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000836061171001</t>
+          <t>20208000908674031001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3750 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>1453637000</v>
+          <t>Оплата за транспортные услуги по договору №111/26</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B39" t="n">
-        <v>131</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>21.07.2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>54671000</v>
+        <v>162338000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №162/26 от 27.07.2026</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>1508308000</v>
+          <t>Mahsulot uchun to'lov, shartn. №269/26, QQS 12%</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B40" t="n">
-        <v>132</v>
-      </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>52418000</v>
-      </c>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>23398000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Chirchiq Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>329565262</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000684702423001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5170 от 27.07.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>1560726000</v>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №2907</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B41" t="n">
-        <v>133</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>19080000</v>
+        <v>38282000</v>
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
+          <t>Olmaliq Polimer XK</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>353092149</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20208000576543652001</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по дог. №83/26 от 22.07.2026, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1633411000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>372985001</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20208000944466651001</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №123/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>53092000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>QQS iyun 2026 uchun</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>347352000</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Shahrisabz Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>273376372</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20208000902639922001</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №1451 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>328401000</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Durdona Polimer XK</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>251039952</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20208000529104342001</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №1590 от 27.07.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>113543000</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Tong Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>274386545</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20208000238126649001</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №5998 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>19080000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>200933985</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>20208000996152972001</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20208000454660415001</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ELEKTR ENERGIYASI UCHUN TO'LOV IYUL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>23924000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Zarafshon Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>323675136</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20208000489984699001</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>01204</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>1541646000</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="B42" t="n">
-        <v>134</v>
-      </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>58719000</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>393733763</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>20208000239026399001</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №8434 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1600365000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="B43" t="n">
-        <v>135</v>
-      </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>252110000</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>393733763</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>20208000239026399001</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Оплата по с/ф№311 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>1852475000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="B44" t="n">
-        <v>136</v>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>533505000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Bekobod Plastik XK</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>235186774</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>20208000214999655001</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №116/26</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>1318970000</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B45" t="n">
-        <v>137</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>1318670000</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B46" t="n">
-        <v>138</v>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>363441000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Saodat Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>241743865</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>20208000542381266001</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №8235</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>955229000</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B47" t="n">
-        <v>139</v>
-      </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>1153699000</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>393733763</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>20208000239026399001</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №7281 от 03.08.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>2108928000</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B48" t="n">
-        <v>140</v>
-      </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>132591000</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Oqtosh Qog'oz MChJ</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>209981350</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>20208000017396323001</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №122/26 от 03.08.2026</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>2241519000</v>
+          <t>Tovarlar uchun to'lov h/f №8280</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B49" t="n">
-        <v>141</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>76273000</v>
+        <v>43911000</v>
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №7514</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>121526000</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Sharq Moy AJ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>327840968</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20208000606117140001</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>00987</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №42/26</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>2165246000</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B50" t="n">
-        <v>142</v>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>112639000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Saodat Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>241743865</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>20208000542381266001</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №85/26 от 28.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>64521000</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sharq Moy AJ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>327840968</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20208000606117140001</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>00987</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №21/26</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>2052607000</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B51" t="n">
-        <v>143</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>350101000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Bekobod Plastik XK</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>235186774</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>20208000214999655001</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Shartnoma №187/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>47665000</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>286289170</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20208000789332193001</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>01121</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №4/26</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>1702506000</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="B52" t="n">
-        <v>144</v>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>250500000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9700)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>16307000349637466417</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9700 bo'yicha navbatdagi to'lov (08.2026)</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>1452006000</v>
+          <t>Оплата за продукцию по договору №116/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="B53" t="n">
-        <v>145</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>395446000</v>
+        <v>300000</v>
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
@@ -2341,117 +2332,120 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>1056560000</v>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>46241</v>
-      </c>
-      <c r="B54" t="n">
-        <v>146</v>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>156135000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>31495000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №187/26</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>900425000</v>
+          <t>Оплата за товар по счет-фактуре №943 от 03.08.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B55" t="n">
-        <v>147</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>30023000</v>
+        <v>455989000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>205823675</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000365489984001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №33/25</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>870402000</v>
+          <t>Оплата за сырье по договору №106/26 от 03.08.2026, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B56" t="n">
-        <v>148</v>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>62696000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>62423000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2461,37 +2455,38 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4279</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>807706000</v>
+          <t>Оплата за товар по счет-фактуре №3723 от 04.08.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B57" t="n">
-        <v>149</v>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>187144000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>37017000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Durdona Metall XK</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>373802480</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000231578328001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2501,197 +2496,192 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №284/26</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>620562000</v>
+          <t>Предоплата за товар по дог. №125/26 от 04.08.2026</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B58" t="n">
-        <v>150</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>187601000</v>
+        <v>395446000</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Termiz Metall XK</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>355787594</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000548335441001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2504</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>432961000</v>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №763</t>
+        </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="B59" t="n">
-        <v>151</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>244206000</v>
+        <v>186862000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Olmaliq Agro MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>378759495</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000833544108001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2513 от 12.08.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>677167000</v>
+          <t>Оплата за товар по счет-фактуре №9492 от 05.08.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="B60" t="n">
-        <v>152</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>238486000</v>
+        <v>28690000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Andijon Metall XK</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>321109101</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000775039704001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №243/26 от 12.08.2026</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>915653000</v>
+          <t>Предоплата за товар по дог. №181/26 от 05.08.2026</t>
+        </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="B61" t="n">
-        <v>153</v>
-      </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>165282000</v>
-      </c>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>250500000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>313862891</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9700)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>16307000349637466417</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №212/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="n">
-        <v>1080935000</v>
+          <t>Kredit shartnomasi L-2025-9700 bo'yicha navbatdagi to'lov (08.2026)</t>
+        </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="B62" t="n">
-        <v>154</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>96959000</v>
+        <v>291697000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>210910127</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000503970463001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2701,157 +2691,161 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2890 от 12.08.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>1177894000</v>
+          <t>Оплата за продукцию по договору №200/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>46247</v>
-      </c>
-      <c r="B63" t="n">
-        <v>155</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>263453000</v>
+        <v>109412000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №134/26 от 13.08.2026</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>1441347000</v>
+          <t>Оплата за товар по счет-фактуре №462 от 06.08.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>46248</v>
-      </c>
-      <c r="B64" t="n">
-        <v>156</v>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>53924000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>33745000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="n">
-        <v>1387423000</v>
+          <t>Shartnoma №10/26 bo'yicha oldindan to'lov</t>
+        </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>46248</v>
-      </c>
-      <c r="B65" t="n">
-        <v>157</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>53924000</v>
+        <v>99483000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>1333499000</v>
+          <t>Оплата за товары согласно счет-фактуре №6684</t>
+        </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>46248</v>
-      </c>
-      <c r="B66" t="n">
-        <v>158</v>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>171825000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>169636000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2861,37 +2855,38 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №73/26</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>1161674000</v>
+          <t>Оплата за товар по с/ф №7361 от 07.08.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>46248</v>
-      </c>
-      <c r="B67" t="n">
-        <v>159</v>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>1431268000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>76800000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2901,317 +2896,325 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №86/26</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>-269594000</v>
+          <t>Mahsulot uchun to'lov, shartnoma №96/26, QQS 12%</t>
+        </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="B68" t="n">
-        <v>160</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>173957000</v>
+        <v>33318000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №145/26 от 17.08.2026</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>-95637000</v>
+          <t>Shartnoma №161/26 bo'yicha oldindan to'lov</t>
+        </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="B69" t="n">
-        <v>161</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>107197000</v>
+        <v>328648000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Andijon Metall XK</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>321109101</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000775039704001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №157/26 от 17.08.2026</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>11560000</v>
+          <t>Оплата за продукцию по дог. №214/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>46252</v>
-      </c>
-      <c r="B70" t="n">
-        <v>162</v>
-      </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>120452000</v>
-      </c>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>30023000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Andijon Metall XK</t>
+          <t>Samarqand Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>321109101</t>
+          <t>386067474</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000775039704001</t>
+          <t>20208000938342519001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №52/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>132012000</v>
+          <t>Арендная плата за август 2026 г. по дог. №98/21</t>
+        </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B71" t="n">
-        <v>163</v>
-      </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>376636000</v>
-      </c>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>41318000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>313862891</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3658 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="n">
-        <v>508648000</v>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №48/26</t>
+        </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B72" t="n">
-        <v>164</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>165475000</v>
+        <v>60754000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>235186774</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000214999655001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №183/26</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>343173000</v>
+          <t>Оплата за упаковочные материалы, с/ф №1123</t>
+        </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>46254</v>
-      </c>
-      <c r="B73" t="n">
-        <v>165</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>235709000</v>
+        <v>357225000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>313862891</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №601 от 20.08.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>578882000</v>
+          <t>Оплата за продукцию по договору №93/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
-        <v>46254</v>
-      </c>
-      <c r="B74" t="n">
-        <v>166</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>118107000</v>
+        <v>80242000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4864</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>696989000</v>
+          <t>Оплата за продукцию по договору №7/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
-        <v>46254</v>
-      </c>
-      <c r="B75" t="n">
-        <v>167</v>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>83344000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>75032000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3221,102 +3224,105 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №281/26, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>613645000</v>
+          <t>Предоплата за товар по дог. №126/26 от 13.08.2026</t>
+        </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B76" t="n">
-        <v>168</v>
-      </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>292911000</v>
-      </c>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>795651000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Chirchiq Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>329565262</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000684702423001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6119</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>906556000</v>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №207/26</t>
+        </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B77" t="n">
-        <v>169</v>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>18764000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>1169108000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000996152972001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>887792000</v>
+          <t>Оплата за товар по с/ф №7771 от 17.08.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B78" t="n">
-        <v>170</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>50816000</v>
+        <v>53924000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
@@ -3341,72 +3347,79 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>НДС ЗА ИЮЛЬ 2026 Г.</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>836976000</v>
+          <t>IJTIMOIY SOLIQ IYUL 2026</t>
+        </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B79" t="n">
-        <v>171</v>
-      </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>515047000</v>
-      </c>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>53924000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>313862891</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №104/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>1352023000</v>
+          <t>JISMONIY SHAXSLAR DAROMAD SOLIG'I IYUL 2026</t>
+        </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B80" t="n">
-        <v>172</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>300000</v>
+        <v>56948000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Zarafshon Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3416,277 +3429,284 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>КОМИССИЯ БАНКА ЗА РАСЧЕТНО-КАССОВОЕ ОБСЛУЖИВАНИЕ ЗА АВГУСТ</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>1351723000</v>
+          <t>Оплата за товары согласно с/ф №4367</t>
+        </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B81" t="n">
-        <v>173</v>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>66752000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>31733000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Tong Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>235186774</t>
+          <t>274386545</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000214999655001</t>
+          <t>20208000238126649001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3295</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>1284971000</v>
+          <t>Предоплата за товар по договору №21/26 от 20.08.2026</t>
+        </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B82" t="n">
-        <v>174</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>320924000</v>
+        <v>33132000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>372985001</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000944466651001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №205/26</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>964047000</v>
+          <t>Предоплата за материалы по договору №190/26</t>
+        </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B83" t="n">
-        <v>175</v>
-      </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>59572000</v>
-      </c>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>46315000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Andijon Metall XK</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>321109101</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000775039704001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3611 от 01.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>1023619000</v>
+          <t>Оплата за транспортные услуги по дог. №18/26</t>
+        </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B84" t="n">
-        <v>176</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>57223000</v>
+        <v>90353000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oqtosh Qog'oz MChJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>209981350</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000017396323001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5797 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>1080842000</v>
+          <t>Предоплата за товар по договору №265/26 от 21.08.2026</t>
+        </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B85" t="n">
-        <v>177</v>
-      </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>53165000</v>
-      </c>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>112057000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Andijon Metall XK</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>321109101</t>
+          <t>372985001</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000775039704001</t>
+          <t>20208000944466651001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №91/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>1134007000</v>
+          <t>Оплата за товары согласно с/ф №5478</t>
+        </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B86" t="n">
-        <v>178</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>18086000</v>
+        <v>115306000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №121/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>1152093000</v>
+          <t>Оплата за товар по счет-фактуре №3786 от 24.08.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B87" t="n">
-        <v>179</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>96074000</v>
+        <v>68155000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oqtosh Qog'oz MChJ</t>
+          <t>Andijon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>209981350</t>
+          <t>398135020</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000017396323001</t>
+          <t>20208000739632308001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3696,152 +3716,161 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №167/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>1248167000</v>
+          <t>Оплата по счет-фактуре №2283 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B88" t="n">
-        <v>180</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>78020000</v>
+        <v>35903000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3642</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>1326187000</v>
+          <t>Mahsulot uchun to'lov, shartnoma №105/26, QQS 12%</t>
+        </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B89" t="n">
-        <v>181</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>52563000</v>
+        <v>39595000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Bog'ishamol Non XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>299782426</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000824202015001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №145/26</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>1273624000</v>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №192/26</t>
+        </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B90" t="n">
-        <v>182</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>121893000</v>
+        <v>49299000</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО С/Ф №3342</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>1151731000</v>
+          <t>Уплата налога на добавленную стоимость за июль</t>
+        </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B91" t="n">
-        <v>183</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>250500000</v>
+        <v>146418000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9700)</t>
+          <t>Zarafshon Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>16307000349637466417</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3851,712 +3880,730 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9700 bo'yicha navbatdagi to'lov (09.2026)</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>901231000</v>
+          <t>Оплата за сырье по дог. №241/26 от 24.08.2026, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B92" t="n">
-        <v>184</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>645877000</v>
+        <v>29646000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №8/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>1547108000</v>
+          <t>Предоплата за товар по договору №290/26 от 25.08.2026</t>
+        </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B93" t="n">
-        <v>185</v>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>361498000</v>
+        <v>30528000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №140 07.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>1908606000</v>
+          <t>Оплата за продукцию по договору №11/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B94" t="n">
-        <v>186</v>
-      </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>80987000</v>
-      </c>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>18764000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000454660415001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9219 от 07.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>1989593000</v>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
+        </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B95" t="n">
-        <v>187</v>
-      </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>66157000</v>
-      </c>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>62917000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Chirchiq Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>329565262</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000684702423001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №19/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>2055750000</v>
+          <t>Предоплата за материалы по договору №205/26</t>
+        </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B96" t="n">
-        <v>188</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>56805000</v>
+        <v>189197000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Andijon Metall XK</t>
+          <t>Durdona Polimer XK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>321109101</t>
+          <t>251039952</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000775039704001</t>
+          <t>20208000529104342001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №44/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>2112555000</v>
+          <t>Оплата по счет-фактуре №7142 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B97" t="n">
-        <v>189</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>50665000</v>
+        <v>76580000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №200/26 от 07.09.2026</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>2163220000</v>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №40/26 ОТ 28.08.2026</t>
+        </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B98" t="n">
-        <v>190</v>
-      </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>29294000</v>
-      </c>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>76327000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №282/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>2192514000</v>
+          <t>Оплата за товары согласно с/ф №855</t>
+        </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B99" t="n">
-        <v>191</v>
-      </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>19034000</v>
-      </c>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>87113000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6444 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>2211548000</v>
+          <t>Оплата за упаковочные материалы, с/ф №4482</t>
+        </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B100" t="n">
-        <v>192</v>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>30501000</v>
+        <v>1070047000</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish Materiallari MChJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>205823675</t>
+          <t>372985001</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000365489984001</t>
+          <t>20208000944466651001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Арендная плата за сентябрь 2026 г. по договору №33/25</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>2181047000</v>
+          <t>Предоплата за материалы по договору №35/26</t>
+        </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B101" t="n">
-        <v>193</v>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>401742000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>233363000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Shahrisabz Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ЗАРАБОТНАЯ ПЛАТА ЗА АВГУСТ 2026 Г. (ПЕРЕЧИСЛЕНИЕ НА ПЛАСТИКОВЫЕ КАРТЫ)</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>1779305000</v>
+          <t>Предоплата за товар по договору №12/26 от 31.08.2026</t>
+        </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B102" t="n">
-        <v>194</v>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v>580975000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>41467000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Termiz Metall XK</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>355787594</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000548335441001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №121/26, QQS BILAN</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>1198330000</v>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3296</t>
+        </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B103" t="n">
-        <v>195</v>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>138297000</v>
+        <v>31742000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2693</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>1336627000</v>
+          <t>Оплата за товар по счет-фактуре №2590 от 31.08.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B104" t="n">
-        <v>196</v>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v>65492000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>31563000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>235186774</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000214999655001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №193/26</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>1271135000</v>
+          <t>Предоплата за товар по договору №203/26 от 31.08.2026</t>
+        </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B105" t="n">
-        <v>197</v>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>506313000</v>
+        <v>31378000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nurafshon Metall Servis MChJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>310830307</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000498088717001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №281/26 от 10.09.2026</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>1777448000</v>
+          <t>Оплата за товар по с/ф №7003 от 31.08.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B106" t="n">
-        <v>198</v>
-      </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>18593000</v>
-      </c>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>393733763</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №45/26 от 10.09.2026</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>1796041000</v>
+          <t>Комиссия за перевод</t>
+        </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B107" t="n">
-        <v>199</v>
-      </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>94744000</v>
-      </c>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>33128000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Chirchiq Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>329565262</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000684702423001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №163/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>1890785000</v>
+          <t>Tovarlar uchun to'lov h/f №5388</t>
+        </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B108" t="n">
-        <v>200</v>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>147461000</v>
+        <v>49159000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Bog'ishamol Non XK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>235186774</t>
+          <t>299782426</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000214999655001</t>
+          <t>20208000824202015001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №147/26 от 11.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>1743324000</v>
+          <t>Предоплата за материалы по договору №186/26</t>
+        </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B109" t="n">
-        <v>201</v>
-      </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>42025000</v>
-      </c>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>76178000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>372985001</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000944466651001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4566,477 +4613,484 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №34/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>1785349000</v>
+          <t>Оплата за транспортные услуги по дог. №204/26</t>
+        </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B110" t="n">
-        <v>202</v>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>21470000</v>
+        <v>159849000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1633 от 14.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>1806819000</v>
+          <t>Mahsulot uchun to'lov, shartn. №181/26, QQS 12%</t>
+        </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B111" t="n">
-        <v>203</v>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>17542000</v>
+        <v>114818000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №181/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>1824361000</v>
+          <t>Предоплата за товар по договору №200/26 от 02.09.2026</t>
+        </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B112" t="n">
-        <v>204</v>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v>132794000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>74525000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Olmaliq Agro MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>235186774</t>
+          <t>378759495</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000214999655001</t>
+          <t>20208000833544108001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №35/26</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>1691567000</v>
+          <t>Оплата по счет-фактуре №5729 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B113" t="n">
-        <v>205</v>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>49496000</v>
+        <v>56650000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4722 от 15.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>1741063000</v>
+          <t>Оплата по с/ф №2451 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B114" t="n">
-        <v>206</v>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>27560000</v>
+        <v>44027000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №112/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>1768623000</v>
+          <t>Оплата за продукцию по договору №145/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B115" t="n">
-        <v>207</v>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>103614000</v>
+        <v>248513000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №74/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>03.09.2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>30899000</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Shahrisabz Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>273376372</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>20208000902639922001</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
           <t>00987</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №408</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>1665009000</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B116" t="n">
-        <v>208</v>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v>54783000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>1610226000</v>
+          <t>Оплата по счет-фактуре №4229 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B117" t="n">
-        <v>209</v>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v>54783000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>56692000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kamalak Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>283030724</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000808871746001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>1555443000</v>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5307</t>
+        </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B118" t="n">
-        <v>210</v>
-      </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>47032000</v>
-      </c>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>05.09.2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>250500000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>393733763</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9700)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>16307000349637466417</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1503 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>1602475000</v>
+          <t>Kredit shartnomasi L-2025-9700 bo'yicha navbatdagi to'lov (09.2026)</t>
+        </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B119" t="n">
-        <v>211</v>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>26960000</v>
+        <v>28827000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Kamalak Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>283030724</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000808871746001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №13/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>1629435000</v>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №3465 07.09.2026, QQS BILAN</t>
+        </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B120" t="n">
-        <v>212</v>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>52978000</v>
+        <v>96216000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Saodat Avto Savdo MChJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>241743865</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000542381266001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1510</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>1576457000</v>
+          <t>Оплата за транспортные услуги по договору №290/26</t>
+        </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B121" t="n">
-        <v>213</v>
-      </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>64288000</v>
-      </c>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>104407000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>372985001</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000944466651001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5046,1033 +5100,2161 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №207/26 от 18.09.2026</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>1640745000</v>
+          <t>Transport xizmatlari uchun to'lov, shartn. №296/26</t>
+        </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B122" t="n">
-        <v>214</v>
-      </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>263431000</v>
-      </c>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>159277000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7282 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>1904176000</v>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГ. №201/26</t>
+        </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B123" t="n">
-        <v>215</v>
-      </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>219711000</v>
-      </c>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>401742000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>313862891</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1889 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>2123887000</v>
+          <t>AVGUST OYI UCHUN ISH HAQI, REESTR №589</t>
+        </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B124" t="n">
-        <v>216</v>
-      </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>67659000</v>
-      </c>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>524805000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>323675136</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000489984699001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4743 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>2191546000</v>
+          <t>Оплата за транспортные услуги по договору №245/26</t>
+        </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B125" t="n">
-        <v>217</v>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>45376000</v>
+        <v>118701000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №284/26 от 21.09.2026</t>
-        </is>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>2236922000</v>
+          <t>Оплата за товар по счет-фактуре №4520 от 08.09.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B126" t="n">
-        <v>218</v>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>21790000</v>
+        <v>84173000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>313862891</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №105/26 от 21.09.2026</t>
-        </is>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>2258712000</v>
+          <t>Предоплата за товар по дог. №183/26 от 08.09.2026</t>
+        </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B127" t="n">
-        <v>219</v>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>17482000</v>
+        <v>44490000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
+          <t>Olmaliq Agro MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>313862891</t>
+          <t>378759495</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>20208000833544108001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №19/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>2276194000</v>
+          <t>Tovar uchun to'lov, hisob-faktura №8736 08.09.2026, QQS bilan</t>
+        </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B128" t="n">
-        <v>220</v>
-      </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>17450000</v>
-      </c>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>30501000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Samarqand Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>386067474</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000938342519001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8988 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="n">
-        <v>2293644000</v>
+          <t>Ijara haqi sentyabr oyi uchun, shartnoma №98/21</t>
+        </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B129" t="n">
-        <v>221</v>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v>41066000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>167247000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Termiz Metall XK</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>355787594</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000548335441001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №61/26</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>2252578000</v>
+          <t>Оплата по счет-фактуре №1236 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B130" t="n">
-        <v>222</v>
-      </c>
-      <c r="C130" s="2" t="n">
-        <v>52661000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>538332000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>2199917000</v>
+          <t>Оплата за товар по счет-фактуре №6258 от 10.09.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B131" t="n">
-        <v>223</v>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1334892000</v>
+        <v>487274000</v>
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Termiz Metall XK</t>
+          <t>Bog'ishamol Non XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>355787594</t>
+          <t>299782426</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000548335441001</t>
+          <t>20208000824202015001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №40/26</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>865025000</v>
+          <t>Xom ashyo uchun to'lov, shartnoma №79/26, QQS bilan</t>
+        </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B132" t="n">
-        <v>224</v>
-      </c>
-      <c r="C132" s="2" t="n">
-        <v>252181000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>89120000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Afrosiyob Mato MChJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>363510399</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000295291043001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №265/26</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>612844000</v>
+          <t>Оплата за товар по с/ф №3468 от 11.09.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B133" t="n">
-        <v>225</v>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>422020000</v>
+        <v>26030000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Andijon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>398135020</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000739632308001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3097 от 23.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>1034864000</v>
+          <t>Оплата за товар по с/ф №6296 от 11.09.2026, в т.ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B134" t="n">
-        <v>226</v>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>37119000</v>
+        <v>60438000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>313862891</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5454</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="n">
-        <v>1071983000</v>
+          <t>Оплата по счет-фактуре №7463 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B135" t="n">
-        <v>227</v>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>210323000</v>
+        <v>43533000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Oqtosh Qog'oz MChJ</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>209981350</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000017396323001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №205/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>1282306000</v>
+          <t>Оплата по счет-фактуре №9126 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B136" t="n">
-        <v>228</v>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>19063000</v>
+        <v>54783000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000996152972001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="n">
-        <v>1263243000</v>
+          <t>Социальный налог за август 2026 г.</t>
+        </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B137" t="n">
-        <v>229</v>
-      </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>190560000</v>
-      </c>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>54783000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Ziyo Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>313862891</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000007893321001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №35/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>1453803000</v>
+          <t>НДФЛ за август 2026</t>
+        </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B138" t="n">
-        <v>230</v>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>37786000</v>
+        <v>846155000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №69/26 от 28.09.2026</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>1491589000</v>
+          <t>Предоплата за товар по дог. №254/26 от 15.09.2026</t>
+        </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B139" t="n">
-        <v>231</v>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>22631000</v>
+        <v>368260000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>286289170</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000789332193001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №130/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>1514220000</v>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1400 ОТ 15.09.2026, В Т.Ч. НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B140" t="n">
-        <v>232</v>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>17924000</v>
+        <v>47610000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №146/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>1532144000</v>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №36/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B141" t="n">
-        <v>233</v>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>181139000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>72817000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bekobod Plastik XK</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>235186774</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000214999655001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №562</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>1351005000</v>
+          <t>Оплата по счет-фактуре №5869 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B142" t="n">
-        <v>234</v>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>44697000</v>
+        <v>65677000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Oqtosh Qog'oz MChJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>209981350</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000017396323001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №186/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>1395702000</v>
+          <t>Оплата по счет-фактуре №6242 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B143" t="n">
-        <v>235</v>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>25711000</v>
+        <v>45845000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon AJ</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>393733763</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000239026399001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9185 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>1421413000</v>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №107/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B144" t="n">
-        <v>236</v>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>28759000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Chirchiq Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>318677402</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000499965505001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>1421113000</v>
+          <t>Оплата за продукцию по договору №118/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B145" t="n">
-        <v>237</v>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>70188000</v>
+        <v>189048000</v>
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Afrosiyob Mato MChJ</t>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>363510399</t>
+          <t>372985001</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000295291043001</t>
+          <t>20208000944466651001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6242</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>1350925000</v>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №188/26</t>
+        </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B146" t="n">
-        <v>238</v>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>314225000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>70495000</v>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Durdona Metall XK</t>
+          <t>Shahrisabz Qog'oz AJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>373802480</t>
+          <t>273376372</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000231578328001</t>
+          <t>20208000902639922001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №272/26</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>1036700000</v>
+          <t>Оплата за продукцию по договору №4/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="n">
-        <v>12838048000</v>
-      </c>
-      <c r="D147" s="4" t="n">
-        <v>12899448000</v>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>49201000</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Navoiy Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>210910127</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20208000503970463001</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №1483 за поставленный товар</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="n">
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>34275000</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Mehnat Non AJ</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>397664827</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>20208000820079628001</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №4369 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>33318000</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Andijon Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>398135020</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>20208000739632308001</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5364</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>32745000</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>286289170</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20208000789332193001</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №205/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>51307000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Уплата налога на добавленную стоимость за август</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>68840000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Sharq Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>334390146</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20208000728720389001</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №153/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>130266000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Bunyodkor Meva-Sabzavot MChJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>372985001</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>20208000944466651001</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №9298</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>669204000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Zarafshon Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>323675136</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000489984699001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №278/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>30737000</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>286289170</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000789332193001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №3345 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>127302000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Chirchiq Dori-Darmon AJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>329565262</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000684702423001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по дог. №46/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>41513000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Shahrisabz Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>273376372</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000902639922001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ПО С/Ф №2294 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>33581000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sharq Moy AJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>327840968</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000606117140001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №1577 от 24.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>93471000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Shahrisabz Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>273376372</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000902639922001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №65/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>78435000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>286289170</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000789332193001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №5881 от 25.09.2026, в т.ч НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>19063000</v>
+      </c>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000454660415001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>112842000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Chirchiq Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>318677402</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000499965505001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №5124 от 28.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>77264000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Shahrisabz Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>273376372</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000902639922001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №216/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>50971000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Sharq Moy AJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>327840968</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000606117140001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №477 28.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>42606000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Shahrisabz Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>273376372</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000902639922001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №20/26 ОТ 28.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>85664000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Oqtosh Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>277941193</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000380922414001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по дог. №213/26 от 28.09.2026, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>97858000</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Zarafshon Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>323675136</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000489984699001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №2257</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>116869000</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Zarafshon Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>323675136</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000489984699001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по дог. №126/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>315574000</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Chirchiq Dori-Darmon AJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>329565262</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000684702423001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №48/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n">
+        <v>199177000</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Shahrisabz Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>273376372</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000902639922001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №5904 от 29.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>49821000</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Qarshi Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>286289170</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000789332193001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №274/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>31642000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Andijon Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>398135020</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000739632308001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №9065 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Bodomzor Bank ATB</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Комиссия за пеевод</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="n">
+        <v>12746779000</v>
+      </c>
+      <c r="D174" s="4" t="n">
+        <v>12808179000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Davr oxiridagi qoldiq:</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="n">
         <v>1036700000</v>
       </c>
-      <c r="D148" s="4" t="n"/>
+      <c r="D175" s="4" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:H8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>